--- a/src/nodes/HPC/compressor_stage_6_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_6_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-14.324593837333119</v>
+        <v>-14.330649982546216</v>
       </c>
       <c r="B1">
-        <v>6.5664914864536419</v>
+        <v>6.5532640816602408</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-13.118663685617547</v>
+        <v>-13.149860339357938</v>
       </c>
       <c r="B2">
-        <v>6.9537029078337564</v>
+        <v>6.8964421863488035</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-12.147958696261171</v>
+        <v>-12.188495668297815</v>
       </c>
       <c r="B3">
-        <v>6.91333933437955</v>
+        <v>6.8398923432759773</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-11.213198661294731</v>
+        <v>-11.260872262697138</v>
       </c>
       <c r="B4">
-        <v>6.8076376672730632</v>
+        <v>6.7218758099437661</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-10.303298497288154</v>
+        <v>-10.356660423743302</v>
       </c>
       <c r="B5">
-        <v>6.6567475556539417</v>
+        <v>6.5612102681652722</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-9.41373422577567</v>
+        <v>-9.4716439304711049</v>
       </c>
       <c r="B6">
-        <v>6.4688923547522474</v>
+        <v>6.3655764360346119</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-8.541920925671505</v>
+        <v>-8.603413386113413</v>
       </c>
       <c r="B7">
-        <v>6.2487707439474134</v>
+        <v>6.1393635278500946</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-7.6863361410483417</v>
+        <v>-7.7505494008644247</v>
       </c>
       <c r="B8">
-        <v>5.9991501316184017</v>
+        <v>5.8851572555689469</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-6.8446044052283925</v>
+        <v>-6.9108378597182609</v>
       </c>
       <c r="B9">
-        <v>5.7243484663311675</v>
+        <v>5.6069910873913731</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-6.0141618721596029</v>
+        <v>-6.0818891616236712</v>
       </c>
       <c r="B10">
-        <v>5.4290261188192979</v>
+        <v>5.3092181756268735</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-5.1925441890433452</v>
+        <v>-5.261406486548081</v>
       </c>
       <c r="B11">
-        <v>5.1176626082999359</v>
+        <v>4.9960226527791258</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-4.3784337563026652</v>
+        <v>-4.44816155849291</v>
       </c>
       <c r="B12">
-        <v>4.7926529703494616</v>
+        <v>4.6696420774971514</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-3.5750004939938842</v>
+        <v>-3.6451074965769359</v>
       </c>
       <c r="B13">
-        <v>4.4482351574976446</v>
+        <v>4.3246967328171326</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.7841389128493619</v>
+        <v>-2.8540090741627031</v>
       </c>
       <c r="B14">
-        <v>4.0809654675126383</v>
+        <v>3.9579717192331803</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.9981543666723516</v>
+        <v>-2.0676962864704893</v>
       </c>
       <c r="B15">
-        <v>3.7048306621627352</v>
+        <v>3.582528682683952</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.2099893730834972</v>
+        <v>-1.2795928497391089</v>
       </c>
       <c r="B16">
-        <v>3.3326593137045433</v>
+        <v>3.2103476835347764</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-0.42472426190211482</v>
+        <v>-0.49443214242378536</v>
       </c>
       <c r="B17">
-        <v>2.9552167723477694</v>
+        <v>2.8328058944131125</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>0.35107940940169691</v>
+        <v>0.28167225546797087</v>
       </c>
       <c r="B18">
-        <v>2.5605759216511119</v>
+        <v>2.4387661654942394</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1.1170729849533858</v>
+        <v>1.0483956199359168</v>
       </c>
       <c r="B19">
-        <v>2.1481030006161119</v>
+        <v>2.0276369448825529</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.8744610342772929</v>
+        <v>1.8068604409816327</v>
       </c>
       <c r="B20">
-        <v>1.7199875871050196</v>
+        <v>1.6014630801647305</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.6244481268977551</v>
+        <v>2.5581892086066933</v>
       </c>
       <c r="B21">
-        <v>1.2784192589800887</v>
+        <v>1.1622894189274482</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.3680242350497909</v>
+        <v>3.3033044214992104</v>
       </c>
       <c r="B22">
-        <v>0.82519751493877513</v>
+        <v>0.71179648323633571</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4.1053209418111472</v>
+        <v>4.0423286130934288</v>
       </c>
       <c r="B23">
-        <v>0.36056153701936011</v>
+        <v>0.25020749307281859</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>4.8362552329702533</v>
+        <v>4.7751843255101294</v>
       </c>
       <c r="B24">
-        <v>-0.11563957190467017</v>
+        <v>-0.22261865710272352</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>5.5607440943155382</v>
+        <v>5.5017941008700895</v>
       </c>
       <c r="B25">
-        <v>-0.60355670895983038</v>
+        <v>-0.7068230728299143</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>6.2786688163213134</v>
+        <v>6.22204718600341</v>
       </c>
       <c r="B26">
-        <v>-1.1034056555885625</v>
+        <v>-1.2026075139033778</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>6.9897679082054207</v>
+        <v>6.9356996465774765</v>
       </c>
       <c r="B27">
-        <v>-1.6156617304970349</v>
+        <v>-1.7104163571377467</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>7.693744183871587</v>
+        <v>7.6424742529689942</v>
       </c>
       <c r="B28">
-        <v>-2.14086513670734</v>
+        <v>-2.2307546336026536</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>8.3903004572235389</v>
+        <v>8.3420937755546678</v>
       </c>
       <c r="B29">
-        <v>-2.6795560772415739</v>
+        <v>-2.7641273743677321</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>9.07929869296212</v>
+        <v>9.0344292395093451</v>
       </c>
       <c r="B30">
-        <v>-3.2319854625114059</v>
+        <v>-3.3107695337395575</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>9.7612374589766553</v>
+        <v>9.7199446892004318</v>
       </c>
       <c r="B31">
-        <v>-3.7972470324868057</v>
+        <v>-3.8698357589724592</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>10.436774473953596</v>
+        <v>10.399252423793497</v>
       </c>
       <c r="B32">
-        <v>-4.3741452345273242</v>
+        <v>-4.4402106205577176</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>11.106567456579388</v>
+        <v>11.072964742454083</v>
       </c>
       <c r="B33">
-        <v>-4.9614845159925034</v>
+        <v>-5.0207786889866037</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>11.771015834965912</v>
+        <v>11.741453238340759</v>
       </c>
       <c r="B34">
-        <v>-5.5585388258461306</v>
+        <v>-5.61086303050252</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>12.429485874926797</v>
+        <v>12.404126680584113</v>
       </c>
       <c r="B35">
-        <v>-6.1664601194689377</v>
+        <v>-6.2115406943573754</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>13.081085551701102</v>
+        <v>13.060153132307748</v>
       </c>
       <c r="B36">
-        <v>-6.7868698538459</v>
+        <v>-6.8243272255552077</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>13.724922840527903</v>
+        <v>13.708700656635264</v>
       </c>
       <c r="B37">
-        <v>-7.4213894859619947</v>
+        <v>-7.4507381691000605</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>14.359472961529674</v>
+        <v>14.348347699555063</v>
       </c>
       <c r="B38">
-        <v>-8.0727906485018952</v>
+        <v>-8.0933631794974232</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>14.980680114362578</v>
+        <v>14.975314238514736</v>
       </c>
       <c r="B39">
-        <v>-8.74844567694908</v>
+        <v>-8.7590883492586</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>15.583855743566183</v>
+        <v>15.585230633826678</v>
       </c>
       <c r="B40">
-        <v>-9.4568770824867325</v>
+        <v>-9.45587388039635</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>16.164311293680075</v>
+        <v>16.173727245803274</v>
       </c>
       <c r="B41">
-        <v>-10.206607376298027</v>
+        <v>-10.191679974923428</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>16.164311293680075</v>
+        <v>16.173727245803274</v>
       </c>
       <c r="B42">
-        <v>-10.206607376298027</v>
+        <v>-10.191679974923428</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>15.363010514954498</v>
+        <v>15.37945441084263</v>
       </c>
       <c r="B43">
-        <v>-9.8583132916735412</v>
+        <v>-9.8307378100290261</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>14.576918078538419</v>
+        <v>14.599102231406659</v>
       </c>
       <c r="B44">
-        <v>-9.48237460126283</v>
+        <v>-9.44443629332337</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>13.801375478955174</v>
+        <v>13.828331067350549</v>
       </c>
       <c r="B45">
-        <v>-9.087259193599337</v>
+        <v>-9.0406809764503233</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>13.031724210728102</v>
+        <v>13.062801278529474</v>
       </c>
       <c r="B46">
-        <v>-8.6814349572165082</v>
+        <v>-8.62737741105374</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>12.263937411388644</v>
+        <v>12.2987617316921</v>
       </c>
       <c r="B47">
-        <v>-8.2722216264570569</v>
+        <v>-8.2113590618108425</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>11.496514790500687</v>
+        <v>11.534815321160995</v>
       </c>
       <c r="B48">
-        <v>-7.8623463189007587</v>
+        <v>-7.7951710455323058</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>10.7285877006362</v>
+        <v>10.770153448152206</v>
       </c>
       <c r="B49">
-        <v>-7.4533879979366606</v>
+        <v>-7.3802863920621578</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>9.9592874943671745</v>
+        <v>10.003967513881781</v>
       </c>
       <c r="B50">
-        <v>-7.0469256269538052</v>
+        <v>-6.9681781312444357</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>9.1880026290873289</v>
+        <v>9.23568844181031</v>
       </c>
       <c r="B51">
-        <v>-6.6440708231112522</v>
+        <v>-6.5598829536390753</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>8.4151499814773381</v>
+        <v>8.4657052443765153</v>
       </c>
       <c r="B52">
-        <v>-6.2440658186481057</v>
+        <v>-6.1546921926696285</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>7.6414035330396226</v>
+        <v>7.6946464562636665</v>
       </c>
       <c r="B53">
-        <v>-5.8456854995734915</v>
+        <v>-5.7514608424755487</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>6.8674372652765889</v>
+        <v>6.923140612155013</v>
       </c>
       <c r="B54">
-        <v>-5.4477047518965227</v>
+        <v>-5.3490438971962853</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>6.0937649087490255</v>
+        <v>6.1516668936378389</v>
       </c>
       <c r="B55">
-        <v>-5.0491897539984985</v>
+        <v>-4.9465684285109193</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>5.3202591902512</v>
+        <v>5.3801070699154954</v>
       </c>
       <c r="B56">
-        <v>-4.6503718537494283</v>
+        <v>-4.5442498182570281</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4.5466325856357486</v>
+        <v>4.60819355709535</v>
       </c>
       <c r="B57">
-        <v>-4.2517736913914952</v>
+        <v>-4.1425755258118118</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3.772597570755309</v>
+        <v>3.835658771284769</v>
       </c>
       <c r="B58">
-        <v>-3.8539179071668834</v>
+        <v>-3.7420330105524711</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>2.9979012473790094</v>
+        <v>3.0622673562792304</v>
       </c>
       <c r="B59">
-        <v>-3.457264200874179</v>
+        <v>-3.3430510224599876</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2.2224292209419394</v>
+        <v>2.2879128666266535</v>
       </c>
       <c r="B60">
-        <v>-3.0620205105375717</v>
+        <v>-2.945823473930457</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.44610172279568</v>
+        <v>1.512521084563069</v>
       </c>
       <c r="B61">
-        <v>-2.6683318337376489</v>
+        <v>-2.5504855679637557</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.66883898429181265</v>
+        <v>0.73601779232450393</v>
       </c>
       <c r="B62">
-        <v>-2.2763431680550008</v>
+        <v>-2.1571725075597605</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-0.10922526914252317</v>
+        <v>-0.041472337901482484</v>
       </c>
       <c r="B63">
-        <v>-1.8858114372462296</v>
+        <v>-1.7656571765557469</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.88710333577794853</v>
+        <v>-0.81902907412122061</v>
       </c>
       <c r="B64">
-        <v>-1.4949412697719935</v>
+        <v>-1.3742631821385982</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.663594019809524</v>
+        <v>-1.5955332943895102</v>
       </c>
       <c r="B65">
-        <v>-1.1015492202689643</v>
+        <v>-0.98095181233259865</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.4374961254323146</v>
+        <v>-2.369865876761156</v>
       </c>
       <c r="B66">
-        <v>-0.70345184337381328</v>
+        <v>-0.58368435516202977</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.2091625733560791</v>
+        <v>-3.1423558029127858</v>
       </c>
       <c r="B67">
-        <v>-0.30129065238868413</v>
+        <v>-0.18306011876021464</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-3.9851627503493656</v>
+        <v>-3.919124469008342</v>
       </c>
       <c r="B68">
-        <v>0.092993004722388917</v>
+        <v>0.20976950830337038</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-4.7705861076503036</v>
+        <v>-4.7049143596109309</v>
       </c>
       <c r="B69">
-        <v>0.47014789792505718</v>
+        <v>0.58616510999821192</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-5.5583858883165433</v>
+        <v>-5.4931598983929808</v>
       </c>
       <c r="B70">
-        <v>0.84298310356559758</v>
+        <v>0.95808724088578723</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-6.3408791635812163</v>
+        <v>-6.2767027783361353</v>
       </c>
       <c r="B71">
-        <v>1.2254640843303082</v>
+        <v>1.3385762370141885</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-7.119974525559865</v>
+        <v>-7.0573218305495464</v>
       </c>
       <c r="B72">
-        <v>1.6141215418849486</v>
+        <v>1.7243915897859696</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-7.8988571218432861</v>
+        <v>-7.837985376125995</v>
       </c>
       <c r="B73">
-        <v>2.0031657492673949</v>
+        <v>2.110125888699006</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-8.6762268010408743</v>
+        <v>-8.6174825579652676</v>
       </c>
       <c r="B74">
-        <v>2.3949600260245276</v>
+        <v>2.4979849602779933</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-9.4496377885784124</v>
+        <v>-9.3935351030743561</v>
       </c>
       <c r="B75">
-        <v>2.7939501212439359</v>
+        <v>2.8921191497598513</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-10.216547116128632</v>
+        <v>-10.163774253082107</v>
       </c>
       <c r="B76">
-        <v>3.2047584556670565</v>
+        <v>3.2968436402035759</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-10.974601384034994</v>
+        <v>-10.926007922962853</v>
       </c>
       <c r="B77">
-        <v>3.631662866052058</v>
+        <v>3.716151767646195</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-11.722302661076945</v>
+        <v>-11.678841206451148</v>
       </c>
       <c r="B78">
-        <v>4.0773861815702253</v>
+        <v>4.1525846422147978</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-12.457091672956395</v>
+        <v>-12.419890310517634</v>
       </c>
       <c r="B79">
-        <v>4.5465804627571247</v>
+        <v>4.6104848357063277</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-13.174472346661572</v>
+        <v>-13.144966872809874</v>
       </c>
       <c r="B80">
-        <v>5.0474183403615438</v>
+        <v>5.0974823159926546</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-13.863389275123721</v>
+        <v>-13.843770821062766</v>
       </c>
       <c r="B81">
-        <v>5.5999955200167708</v>
+        <v>5.6323407940060015</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-14.324593837333119</v>
+        <v>-14.330649982546216</v>
       </c>
       <c r="B82">
-        <v>6.5664914864536419</v>
+        <v>6.5532640816602408</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-17.291842877133803</v>
+        <v>-17.244939741920671</v>
       </c>
       <c r="B1">
-        <v>5.7179516804446173</v>
+        <v>5.8578882547303222</v>
       </c>
       <c r="C1">
         <v>218.7117598010542</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-16.18643512939947</v>
+        <v>-16.175711993431822</v>
       </c>
       <c r="B2">
-        <v>5.7980485344610981</v>
+        <v>5.8329501689661587</v>
       </c>
       <c r="C2">
         <v>218.7117598010542</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-15.163751223563859</v>
+        <v>-15.168128029802613</v>
       </c>
       <c r="B3">
-        <v>5.6567791458259524</v>
+        <v>5.6470455385272249</v>
       </c>
       <c r="C3">
         <v>218.7117598010542</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-14.153963834208161</v>
+        <v>-14.170537738689852</v>
       </c>
       <c r="B4">
-        <v>5.480999109100388</v>
+        <v>5.4350450585675807</v>
       </c>
       <c r="C4">
         <v>218.7117598010542</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-13.153192025934038</v>
+        <v>-13.180069994366964</v>
       </c>
       <c r="B5">
-        <v>5.28109367800797</v>
+        <v>5.2044459194136588</v>
       </c>
       <c r="C5">
         <v>218.7117598010542</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-12.159853767205076</v>
+        <v>-12.195554142211636</v>
       </c>
       <c r="B6">
-        <v>5.0612963161902655</v>
+        <v>4.9583049779730812</v>
       </c>
       <c r="C6">
         <v>218.7117598010542</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-11.173046232975123</v>
+        <v>-11.21632195556951</v>
       </c>
       <c r="B7">
-        <v>4.82402295336783</v>
+        <v>4.6983671325491825</v>
       </c>
       <c r="C7">
         <v>218.7117598010542</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-10.192238769543716</v>
+        <v>-10.241980511718987</v>
       </c>
       <c r="B8">
-        <v>4.57069360114944</v>
+        <v>4.42565839757251</v>
       </c>
       <c r="C8">
         <v>218.7117598010542</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-9.2166015228173652</v>
+        <v>-9.2719156158047227</v>
       </c>
       <c r="B9">
-        <v>4.3035289214193773</v>
+        <v>4.1417825815023779</v>
       </c>
       <c r="C9">
         <v>218.7117598010542</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-8.245238487148292</v>
+        <v>-8.30546416143477</v>
       </c>
       <c r="B10">
-        <v>4.0249265954154874</v>
+        <v>3.8484712124223694</v>
       </c>
       <c r="C10">
         <v>218.7117598010542</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-7.2772882510646308</v>
+        <v>-7.3419886682045492</v>
       </c>
       <c r="B11">
-        <v>3.7371917315143537</v>
+        <v>3.547388902884387</v>
       </c>
       <c r="C11">
         <v>218.7117598010542</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-6.3122911118919589</v>
+        <v>-6.38114880861411</v>
       </c>
       <c r="B12">
-        <v>3.4415544787448127</v>
+        <v>3.2394243287192244</v>
       </c>
       <c r="C12">
         <v>218.7117598010542</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-5.3513596079697283</v>
+        <v>-5.4237672407947333</v>
       </c>
       <c r="B13">
-        <v>3.1350377216059759</v>
+        <v>2.9224293344049403</v>
       </c>
       <c r="C13">
         <v>218.7117598010542</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-4.3951592206557475</v>
+        <v>-4.4703359647426613</v>
       </c>
       <c r="B14">
-        <v>2.8158606541735622</v>
+        <v>2.5951191912449416</v>
       </c>
       <c r="C14">
         <v>218.7117598010542</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-3.4409949623673786</v>
+        <v>-3.5188613622828186</v>
       </c>
       <c r="B15">
-        <v>2.4912349733594623</v>
+        <v>2.2626997091967729</v>
       </c>
       <c r="C15">
         <v>218.7117598010542</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.486395003641134</v>
+        <v>-2.56751489667838</v>
       </c>
       <c r="B16">
-        <v>2.1677752123895213</v>
+        <v>1.9299456314240444</v>
       </c>
       <c r="C16">
         <v>218.7117598010542</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.5331406164305321</v>
+        <v>-1.6176139751168515</v>
       </c>
       <c r="B17">
-        <v>1.8407147469092349</v>
+        <v>1.593416895260485</v>
       </c>
       <c r="C17">
         <v>218.7117598010542</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.58353197083856423</v>
+        <v>-0.67085984335536342</v>
       </c>
       <c r="B18">
-        <v>1.503898398417812</v>
+        <v>1.2486711444849303</v>
       </c>
       <c r="C18">
         <v>218.7117598010542</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.36230827185094344</v>
+        <v>0.27265684249481409</v>
       </c>
       <c r="B19">
-        <v>1.1569979294096509</v>
+        <v>0.89547165448649979</v>
       </c>
       <c r="C19">
         <v>218.7117598010542</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.3048018275589655</v>
+        <v>1.2132480737338873</v>
       </c>
       <c r="B20">
-        <v>0.80114183762794378</v>
+        <v>0.53463310855688073</v>
       </c>
       <c r="C20">
         <v>218.7117598010542</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.2443704122064636</v>
+        <v>2.1512258416620496</v>
       </c>
       <c r="B21">
-        <v>0.43745862081588682</v>
+        <v>0.16697018998776597</v>
       </c>
       <c r="C21">
         <v>218.7117598010542</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.1813606691462493</v>
+        <v>3.0868465891765005</v>
       </c>
       <c r="B22">
-        <v>0.06687588502742188</v>
+        <v>-0.20684746798593606</v>
       </c>
       <c r="C22">
         <v>218.7117598010542</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4.1158189514584764</v>
+        <v>4.0201445655624113</v>
       </c>
       <c r="B23">
-        <v>-0.31048233044050627</v>
+        <v>-0.58673043235642774</v>
       </c>
       <c r="C23">
         <v>218.7117598010542</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>5.0477165396551369</v>
+        <v>4.9510984717019468</v>
       </c>
       <c r="B24">
-        <v>-0.69469287798020263</v>
+        <v>-0.97273432017268935</v>
       </c>
       <c r="C24">
         <v>218.7117598010542</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>5.97702471424823</v>
+        <v>5.8796870084772808</v>
       </c>
       <c r="B25">
-        <v>-1.085832609983977</v>
+        <v>-1.3649147484837061</v>
       </c>
       <c r="C25">
         <v>218.7117598010542</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>6.9037023698824118</v>
+        <v>6.8058796969091278</v>
       </c>
       <c r="B26">
-        <v>-1.48401152301213</v>
+        <v>-1.7633513051342398</v>
       </c>
       <c r="C26">
         <v>218.7117598010542</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>7.8276588577330211</v>
+        <v>7.7296093385724127</v>
       </c>
       <c r="B27">
-        <v>-1.8894721902969618</v>
+        <v>-2.1682194611521886</v>
       </c>
       <c r="C27">
         <v>218.7117598010542</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>8.7487911431080541</v>
+        <v>8.6507995551806</v>
       </c>
       <c r="B28">
-        <v>-2.3024903292387626</v>
+        <v>-2.5797186583612257</v>
       </c>
       <c r="C28">
         <v>218.7117598010542</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>9.6669961913155156</v>
+        <v>9.5693739684471684</v>
       </c>
       <c r="B29">
-        <v>-2.7233416572378295</v>
+        <v>-2.9980483385850323</v>
       </c>
       <c r="C29">
         <v>218.7117598010542</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>10.582226863758619</v>
+        <v>10.485297526562428</v>
       </c>
       <c r="B30">
-        <v>-3.1521523156074158</v>
+        <v>-3.423300030413269</v>
       </c>
       <c r="C30">
         <v>218.7117598010542</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>11.494659606221417</v>
+        <v>11.398700483624063</v>
       </c>
       <c r="B31">
-        <v>-3.5884501413126166</v>
+        <v>-3.8551336094995361</v>
       </c>
       <c r="C31">
         <v>218.7117598010542</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>12.404526760583197</v>
+        <v>12.309754420206618</v>
       </c>
       <c r="B32">
-        <v>-4.0316133952314956</v>
+        <v>-4.2931010382634271</v>
       </c>
       <c r="C32">
         <v>218.7117598010542</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>13.312060668723232</v>
+        <v>13.218630916884623</v>
       </c>
       <c r="B33">
-        <v>-4.48102033824211</v>
+        <v>-4.7367542791245283</v>
       </c>
       <c r="C33">
         <v>218.7117598010542</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>14.217403302650608</v>
+        <v>14.125434690521713</v>
       </c>
       <c r="B34">
-        <v>-4.9362910579819106</v>
+        <v>-5.1858198915121738</v>
       </c>
       <c r="C34">
         <v>218.7117598010542</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>15.120335154893706</v>
+        <v>15.030003003137992</v>
       </c>
       <c r="B35">
-        <v>-5.3980129491259241</v>
+        <v>-5.640722822894686</v>
       </c>
       <c r="C35">
         <v>218.7117598010542</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>16.0205463481107</v>
+        <v>15.932106253042644</v>
       </c>
       <c r="B36">
-        <v>-5.8670152331085639</v>
+        <v>-6.1020626177501276</v>
       </c>
       <c r="C36">
         <v>218.7117598010542</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>16.917727004959787</v>
+        <v>16.831514838544873</v>
       </c>
       <c r="B37">
-        <v>-6.3441271313642487</v>
+        <v>-6.5704388205565651</v>
       </c>
       <c r="C37">
         <v>218.7117598010542</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>17.811345653626706</v>
+        <v>17.727835232464905</v>
       </c>
       <c r="B38">
-        <v>-6.8307708447470068</v>
+        <v>-7.0468790241282235</v>
       </c>
       <c r="C38">
         <v>218.7117598010542</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>18.699984444407455</v>
+        <v>18.620018205667108</v>
       </c>
       <c r="B39">
-        <v>-7.3307404917892978</v>
+        <v>-7.53412301462396</v>
       </c>
       <c r="C39">
         <v>218.7117598010542</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>19.582003933125542</v>
+        <v>19.506850603526839</v>
       </c>
       <c r="B40">
-        <v>-7.8484231704431844</v>
+        <v>-8.03533862653878</v>
       </c>
       <c r="C40">
         <v>218.7117598010542</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>20.455764675604517</v>
+        <v>20.387119271419483</v>
       </c>
       <c r="B41">
-        <v>-8.3882059786607375</v>
+        <v>-8.5536936943676967</v>
       </c>
       <c r="C41">
         <v>218.7117598010542</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>20.455764675604517</v>
+        <v>20.387119271419483</v>
       </c>
       <c r="B42">
-        <v>-8.3882059786607375</v>
+        <v>-8.5536936943676967</v>
       </c>
       <c r="C42">
         <v>218.7117598010542</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>19.504616185673783</v>
+        <v>19.449608749207925</v>
       </c>
       <c r="B43">
-        <v>-8.0555102022766771</v>
+        <v>-8.1848106863980536</v>
       </c>
       <c r="C43">
         <v>218.7117598010542</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>18.558499683086627</v>
+        <v>18.515365332795703</v>
       </c>
       <c r="B44">
-        <v>-7.7093489955432632</v>
+        <v>-7.8073964902023123</v>
       </c>
       <c r="C44">
         <v>218.7117598010542</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>17.615779250374779</v>
+        <v>17.583179470626128</v>
       </c>
       <c r="B45">
-        <v>-7.3541000190590005</v>
+        <v>-7.4246095318104359</v>
       </c>
       <c r="C45">
         <v>218.7117598010542</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>16.674818970069989</v>
+        <v>16.651841611142522</v>
       </c>
       <c r="B46">
-        <v>-6.9941409334224032</v>
+        <v>-7.0396082372524</v>
       </c>
       <c r="C46">
         <v>218.7117598010542</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>15.734204395827161</v>
+        <v>15.720306002257136</v>
       </c>
       <c r="B47">
-        <v>-6.6332567498909194</v>
+        <v>-6.6551233132901686</v>
       </c>
       <c r="C47">
         <v>218.7117598010542</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>14.793406965793855</v>
+        <v>14.788182089758053</v>
       </c>
       <c r="B48">
-        <v>-6.2728618823577724</v>
+        <v>-6.2721745896136927</v>
       </c>
       <c r="C48">
         <v>218.7117598010542</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>13.852119589240797</v>
+        <v>13.855243118902303</v>
       </c>
       <c r="B49">
-        <v>-5.9137780953751262</v>
+        <v>-5.8913541766449145</v>
       </c>
       <c r="C49">
         <v>218.7117598010542</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>12.910035175438727</v>
+        <v>12.921262334946935</v>
       </c>
       <c r="B50">
-        <v>-5.5568271534951528</v>
+        <v>-5.5132541848057892</v>
       </c>
       <c r="C50">
         <v>218.7117598010542</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>11.966936866688322</v>
+        <v>11.986079707056781</v>
       </c>
       <c r="B51">
-        <v>-5.2025893606905269</v>
+        <v>-5.1382924925675075</v>
       </c>
       <c r="C51">
         <v>218.7117598010542</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>11.022968737410047</v>
+        <v>11.049802100027948</v>
       </c>
       <c r="B52">
-        <v>-4.8506791786159624</v>
+        <v>-4.7661900505982668</v>
       </c>
       <c r="C52">
         <v>218.7117598010542</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>10.078365095054327</v>
+        <v>10.11260310256435</v>
       </c>
       <c r="B53">
-        <v>-4.5004696083466866</v>
+        <v>-4.3964935776155123</v>
       </c>
       <c r="C53">
         <v>218.7117598010542</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>9.1333602470715611</v>
+        <v>9.17465630336988</v>
       </c>
       <c r="B54">
-        <v>-4.15133365095792</v>
+        <v>-4.0287497923366846</v>
       </c>
       <c r="C54">
         <v>218.7117598010542</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>8.1881324734614314</v>
+        <v>8.2360938304719866</v>
       </c>
       <c r="B55">
-        <v>-3.8027942351149537</v>
+        <v>-3.6626136771402913</v>
       </c>
       <c r="C55">
         <v>218.7117598010542</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>7.2426359444206279</v>
+        <v>7.296881969192258</v>
       </c>
       <c r="B56">
-        <v>-3.4549739998433382</v>
+        <v>-3.2981732690490815</v>
       </c>
       <c r="C56">
         <v>218.7117598010542</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>6.2967688026950892</v>
+        <v>6.3569455441757992</v>
       </c>
       <c r="B57">
-        <v>-3.1081455117586856</v>
+        <v>-2.9356248687468631</v>
       </c>
       <c r="C57">
         <v>218.7117598010542</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5.35042919103077</v>
+        <v>5.4162093800677331</v>
       </c>
       <c r="B58">
-        <v>-2.7625813374766128</v>
+        <v>-2.5751647769174464</v>
       </c>
       <c r="C58">
         <v>218.7117598010542</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4.40352750800521</v>
+        <v>4.4746073485233762</v>
       </c>
       <c r="B59">
-        <v>-2.4185212474160087</v>
+        <v>-2.2169656703549632</v>
       </c>
       <c r="C59">
         <v>218.7117598010542</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3.4560231755223754</v>
+        <v>3.5321095092388859</v>
       </c>
       <c r="B60">
-        <v>-2.076073827208877</v>
+        <v>-1.8611057302948453</v>
       </c>
       <c r="C60">
         <v>218.7117598010542</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2.5078878713178248</v>
+        <v>2.588694968920616</v>
       </c>
       <c r="B61">
-        <v>-1.7353148662904943</v>
+        <v>-1.5076395140828434</v>
       </c>
       <c r="C61">
         <v>218.7117598010542</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1.5590932731271254</v>
+        <v>1.64434283427493</v>
       </c>
       <c r="B62">
-        <v>-1.3963201540961407</v>
+        <v>-1.156621579064713</v>
       </c>
       <c r="C62">
         <v>218.7117598010542</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.60968599627022058</v>
+        <v>0.699087622504762</v>
       </c>
       <c r="B63">
-        <v>-1.058964949583957</v>
+        <v>-0.80796179263584</v>
       </c>
       <c r="C63">
         <v>218.7117598010542</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.33998759359545139</v>
+        <v>-0.246814507200677</v>
       </c>
       <c r="B64">
-        <v>-0.72232238980352292</v>
+        <v>-0.460991262390137</v>
       </c>
       <c r="C64">
         <v>218.7117598010542</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.2895061932280632</v>
+        <v>-1.1930519851555916</v>
       </c>
       <c r="B65">
-        <v>-0.38526508132728415</v>
+        <v>-0.11489640597115196</v>
       </c>
       <c r="C65">
         <v>218.7117598010542</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.2384484993858</v>
+        <v>-2.1393132416742</v>
       </c>
       <c r="B66">
-        <v>-0.046665630727681442</v>
+        <v>0.23113635897757115</v>
       </c>
       <c r="C66">
         <v>218.7117598010542</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.1869376945907706</v>
+        <v>-3.0856894653918219</v>
       </c>
       <c r="B67">
-        <v>0.2931463296733986</v>
+        <v>0.57686891729851464</v>
       </c>
       <c r="C67">
         <v>218.7117598010542</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-4.13727490442082</v>
+        <v>-4.0338828782282334</v>
       </c>
       <c r="B68">
-        <v>0.62801306455629868</v>
+        <v>0.91785636377828028</v>
       </c>
       <c r="C68">
         <v>218.7117598010542</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-5.0912425130315508</v>
+        <v>-4.9852120236542445</v>
       </c>
       <c r="B69">
-        <v>0.9531649733508456</v>
+        <v>1.2506556686453703</v>
       </c>
       <c r="C69">
         <v>218.7117598010542</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-6.0463699958338495</v>
+        <v>-5.9378496980603446</v>
       </c>
       <c r="B70">
-        <v>1.2752130974825588</v>
+        <v>1.5800380939517571</v>
       </c>
       <c r="C70">
         <v>218.7117598010542</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-6.99996378891125</v>
+        <v>-6.8898037377626142</v>
       </c>
       <c r="B71">
-        <v>1.6013653241801293</v>
+        <v>1.9112056516335427</v>
       </c>
       <c r="C71">
         <v>218.7117598010542</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-7.9526910797825954</v>
+        <v>-7.841567885859865</v>
       </c>
       <c r="B72">
-        <v>1.9298362818892429</v>
+        <v>2.242869061339869</v>
       </c>
       <c r="C72">
         <v>218.7117598010542</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-8.9056662488116558</v>
+        <v>-8.7939666823909128</v>
       </c>
       <c r="B73">
-        <v>2.2576439259133263</v>
+        <v>2.5728752534417834</v>
       </c>
       <c r="C73">
         <v>218.7117598010542</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-9.85843169630666</v>
+        <v>-9.7466619483719086</v>
       </c>
       <c r="B74">
-        <v>2.5860127777697834</v>
+        <v>2.9021072934849261</v>
       </c>
       <c r="C74">
         <v>218.7117598010542</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-10.810128245527197</v>
+        <v>-10.699018486515776</v>
       </c>
       <c r="B75">
-        <v>2.9172419657683264</v>
+        <v>3.232223832259804</v>
       </c>
       <c r="C75">
         <v>218.7117598010542</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-11.759862391593906</v>
+        <v>-11.650375745345224</v>
       </c>
       <c r="B76">
-        <v>3.2537224791739163</v>
+        <v>3.5649497263617982</v>
       </c>
       <c r="C76">
         <v>218.7117598010542</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-12.706806917193687</v>
+        <v>-12.600122223876458</v>
       </c>
       <c r="B77">
-        <v>3.5976679239344049</v>
+        <v>3.9018817499125937</v>
       </c>
       <c r="C77">
         <v>218.7117598010542</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-13.650434083417501</v>
+        <v>-13.547867977289894</v>
       </c>
       <c r="B78">
-        <v>3.9504905117739435</v>
+        <v>4.2440381413342054</v>
       </c>
       <c r="C78">
         <v>218.7117598010542</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-14.589844105874517</v>
+        <v>-14.492947885422291</v>
       </c>
       <c r="B79">
-        <v>4.314598035720774</v>
+        <v>4.59315568714474</v>
       </c>
       <c r="C79">
         <v>218.7117598010542</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-15.523458243871046</v>
+        <v>-15.434194655746859</v>
       </c>
       <c r="B80">
-        <v>4.6942151532311254</v>
+        <v>4.95228246502294</v>
       </c>
       <c r="C80">
         <v>218.7117598010542</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-16.447399046092919</v>
+        <v>-16.368740722058039</v>
       </c>
       <c r="B81">
-        <v>5.0997177947354393</v>
+        <v>5.32890637054148</v>
       </c>
       <c r="C81">
         <v>218.7117598010542</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-17.291842877133803</v>
+        <v>-17.244939741920671</v>
       </c>
       <c r="B82">
-        <v>5.7179516804446173</v>
+        <v>5.8578882547303222</v>
       </c>
       <c r="C82">
         <v>218.7117598010542</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-19.728809724786526</v>
+        <v>-19.660990497427413</v>
       </c>
       <c r="B1">
-        <v>5.33186986901567</v>
+        <v>5.5767573120064879</v>
       </c>
       <c r="C1">
         <v>240.80649437282904</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-18.555113397715711</v>
+        <v>-18.512417735555605</v>
       </c>
       <c r="B2">
-        <v>5.3119559501293745</v>
+        <v>5.4623165525140251</v>
       </c>
       <c r="C2">
         <v>240.80649437282904</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-17.426709112518338</v>
+        <v>-17.395625842384753</v>
       </c>
       <c r="B3">
-        <v>5.13928084103071</v>
+        <v>5.2453789651061733</v>
       </c>
       <c r="C3">
         <v>240.80649437282904</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-16.305404743756942</v>
+        <v>-16.284087470870293</v>
       </c>
       <c r="B4">
-        <v>4.9426591037760428</v>
+        <v>5.0114981874340039</v>
       </c>
       <c r="C4">
         <v>240.80649437282904</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-15.189078127338165</v>
+        <v>-15.176328484283951</v>
       </c>
       <c r="B5">
-        <v>4.7292483823866851</v>
+        <v>4.765428474014108</v>
       </c>
       <c r="C5">
         <v>240.80649437282904</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-14.07686447524576</v>
+        <v>-14.071748092338334</v>
       </c>
       <c r="B6">
-        <v>4.5019654375380158</v>
+        <v>4.5091074401860425</v>
       </c>
       <c r="C6">
         <v>240.80649437282904</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-12.968270457928041</v>
+        <v>-12.970003519484456</v>
       </c>
       <c r="B7">
-        <v>4.2624741732264937</v>
+        <v>4.2436405751291231</v>
       </c>
       <c r="C7">
         <v>240.80649437282904</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-11.863006288412279</v>
+        <v>-11.870893370248007</v>
       </c>
       <c r="B8">
-        <v>4.0117519841782574</v>
+        <v>3.9696774015945322</v>
       </c>
       <c r="C8">
         <v>240.80649437282904</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-10.760618485123734</v>
+        <v>-10.774102562461639</v>
       </c>
       <c r="B9">
-        <v>3.7513283749647632</v>
+        <v>3.6882340945329708</v>
       </c>
       <c r="C9">
         <v>240.80649437282904</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-9.6606173627166925</v>
+        <v>-9.6792908732456056</v>
       </c>
       <c r="B10">
-        <v>3.4828549583892103</v>
+        <v>3.4004079104822176</v>
       </c>
       <c r="C10">
         <v>240.80649437282904</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-8.5625321153635241</v>
+        <v>-8.5861312035635748</v>
       </c>
       <c r="B11">
-        <v>3.2079196703364219</v>
+        <v>3.1072537801288451</v>
       </c>
       <c r="C11">
         <v>240.80649437282904</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-7.46611163480068</v>
+        <v>-7.4944490555428942</v>
       </c>
       <c r="B12">
-        <v>2.9273694498187446</v>
+        <v>2.8093344784741481</v>
       </c>
       <c r="C12">
         <v>240.80649437282904</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-6.3719647235028711</v>
+        <v>-6.4046672121222583</v>
       </c>
       <c r="B13">
-        <v>2.639150925276986</v>
+        <v>2.5052864836295279</v>
       </c>
       <c r="C13">
         <v>240.80649437282904</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-5.280455640544143</v>
+        <v>-5.3170386085955768</v>
       </c>
       <c r="B14">
-        <v>2.342035522167035</v>
+        <v>2.1942940512068203</v>
       </c>
       <c r="C14">
         <v>240.80649437282904</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-4.1901105606576223</v>
+        <v>-4.2305395088663049</v>
       </c>
       <c r="B15">
-        <v>2.0409941645766354</v>
+        <v>1.8796588437095056</v>
       </c>
       <c r="C15">
         <v>240.80649437282904</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.09957769831043</v>
+        <v>-3.1442309470709708</v>
       </c>
       <c r="B16">
-        <v>1.7405861604630601</v>
+        <v>1.5644091302334557</v>
       </c>
       <c r="C16">
         <v>240.80649437282904</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.0098315112465532</v>
+        <v>-2.058789709668817</v>
       </c>
       <c r="B17">
-        <v>1.4375248546298312</v>
+        <v>1.2463621993524685</v>
       </c>
       <c r="C17">
         <v>240.80649437282904</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.922130248804069</v>
+        <v>-0.97508970329078648</v>
       </c>
       <c r="B18">
-        <v>1.1275664183927241</v>
+        <v>0.92269960521443473</v>
       </c>
       <c r="C18">
         <v>240.80649437282904</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.16345891657939493</v>
+        <v>0.10682243706804082</v>
       </c>
       <c r="B19">
-        <v>0.81048429227029284</v>
+        <v>0.5932709447857033</v>
       </c>
       <c r="C19">
         <v>240.80649437282904</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.2471665816913389</v>
+        <v>1.1871068943215692</v>
       </c>
       <c r="B20">
-        <v>0.48705623408178239</v>
+        <v>0.25859282573723325</v>
       </c>
       <c r="C20">
         <v>240.80649437282904</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.32922334331925</v>
+        <v>2.2659238513836892</v>
       </c>
       <c r="B21">
-        <v>0.15806000164644124</v>
+        <v>-0.080818144260012215</v>
       </c>
       <c r="C21">
         <v>240.80649437282904</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.4098187577620642</v>
+        <v>3.3434049801010892</v>
       </c>
       <c r="B22">
-        <v>-0.17586506874973332</v>
+        <v>-0.42453730889038921</v>
       </c>
       <c r="C22">
         <v>240.80649437282904</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4.4889782193644505</v>
+        <v>4.4195679080515831</v>
       </c>
       <c r="B23">
-        <v>-0.51463332695372643</v>
+        <v>-0.77250781725950757</v>
       </c>
       <c r="C23">
         <v>240.80649437282904</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>5.566686081982513</v>
+        <v>5.4944017517457677</v>
       </c>
       <c r="B24">
-        <v>-0.8582975443457711</v>
+        <v>-1.1247647698282928</v>
       </c>
       <c r="C24">
         <v>240.80649437282904</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>6.6429266994723646</v>
+        <v>6.56789562769425</v>
       </c>
       <c r="B25">
-        <v>-1.206910492306102</v>
+        <v>-1.4813432670576729</v>
       </c>
       <c r="C25">
         <v>240.80649437282904</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>7.7176776715244326</v>
+        <v>7.6400339558845554</v>
       </c>
       <c r="B26">
-        <v>-1.5605477226934683</v>
+        <v>-1.8422935562165881</v>
       </c>
       <c r="C26">
         <v>240.80649437282904</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>8.7908895811664767</v>
+        <v>8.7107823702119482</v>
       </c>
       <c r="B27">
-        <v>-1.9193759092807008</v>
+        <v>-2.2077264718060579</v>
       </c>
       <c r="C27">
         <v>240.80649437282904</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>9.8625062572605646</v>
+        <v>9.780101808048606</v>
       </c>
       <c r="B28">
-        <v>-2.2835845063191424</v>
+        <v>-2.5777679951351131</v>
       </c>
       <c r="C28">
         <v>240.80649437282904</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>10.932471528668769</v>
+        <v>10.847953206766713</v>
       </c>
       <c r="B29">
-        <v>-2.6533629680601374</v>
+        <v>-2.9525441075127858</v>
       </c>
       <c r="C29">
         <v>240.80649437282904</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>12.000759817816144</v>
+        <v>11.914318747888391</v>
       </c>
       <c r="B30">
-        <v>-3.0287975626565733</v>
+        <v>-3.3321122755073591</v>
       </c>
       <c r="C30">
         <v>240.80649437282904</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>13.067467921379604</v>
+        <v>12.97926558953548</v>
       </c>
       <c r="B31">
-        <v>-3.4095618138674855</v>
+        <v>-3.7162559067241019</v>
       </c>
       <c r="C31">
         <v>240.80649437282904</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>14.13272322959906</v>
+        <v>14.042882133979772</v>
       </c>
       <c r="B32">
-        <v>-3.795226059353455</v>
+        <v>-4.1046898940275405</v>
       </c>
       <c r="C32">
         <v>240.80649437282904</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>15.196653132714406</v>
+        <v>15.105256783493049</v>
       </c>
       <c r="B33">
-        <v>-4.1853606367750595</v>
+        <v>-4.497129130282195</v>
       </c>
       <c r="C33">
         <v>240.80649437282904</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>16.259335613979019</v>
+        <v>16.166443618139539</v>
       </c>
       <c r="B34">
-        <v>-4.5797025238858371</v>
+        <v>-4.8933992012803182</v>
       </c>
       <c r="C34">
         <v>240.80649437282904</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>17.320651028700105</v>
+        <v>17.226359429153192</v>
       </c>
       <c r="B35">
-        <v>-4.9786552588111421</v>
+        <v>-5.2937684645250842</v>
       </c>
       <c r="C35">
         <v>240.80649437282904</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>18.380430325198351</v>
+        <v>18.284886685560419</v>
       </c>
       <c r="B36">
-        <v>-5.3827890197692891</v>
+        <v>-5.6986159704473964</v>
       </c>
       <c r="C36">
         <v>240.80649437282904</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>19.438504451794458</v>
+        <v>19.341907856387618</v>
       </c>
       <c r="B37">
-        <v>-5.7926739849785962</v>
+        <v>-6.1083207694781612</v>
       </c>
       <c r="C37">
         <v>240.80649437282904</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>20.494583173295325</v>
+        <v>20.397221235038803</v>
       </c>
       <c r="B38">
-        <v>-6.2092890609247275</v>
+        <v>-6.5235333877705282</v>
       </c>
       <c r="C38">
         <v>240.80649437282904</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>21.547891520452719</v>
+        <v>21.450288412428332</v>
       </c>
       <c r="B39">
-        <v>-6.6352480671627507</v>
+        <v>-6.9459902543666088</v>
       </c>
       <c r="C39">
         <v>240.80649437282904</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>22.597533340504615</v>
+        <v>22.500486803848215</v>
       </c>
       <c r="B40">
-        <v>-7.0735735515150875</v>
+        <v>-7.3776992740307641</v>
       </c>
       <c r="C40">
         <v>240.80649437282904</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>23.642612480689014</v>
+        <v>23.54719382459043</v>
       </c>
       <c r="B41">
-        <v>-7.5272880618041587</v>
+        <v>-7.8206683515273516</v>
       </c>
       <c r="C41">
         <v>240.80649437282904</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>23.642612480689014</v>
+        <v>23.54719382459043</v>
       </c>
       <c r="B42">
-        <v>-7.5272880618041587</v>
+        <v>-7.8206683515273516</v>
       </c>
       <c r="C42">
         <v>240.80649437282904</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>22.555205388821037</v>
+        <v>22.471086973821954</v>
       </c>
       <c r="B43">
-        <v>-7.2163374458103311</v>
+        <v>-7.4725169880239992</v>
       </c>
       <c r="C43">
         <v>240.80649437282904</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>21.470505108025044</v>
+        <v>21.396537940666231</v>
       </c>
       <c r="B44">
-        <v>-6.8962572859953024</v>
+        <v>-7.1193414898665432</v>
       </c>
       <c r="C44">
         <v>240.80649437282904</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>20.387616301402083</v>
+        <v>20.322924990429307</v>
       </c>
       <c r="B45">
-        <v>-6.5700673784350547</v>
+        <v>-6.7631470204297095</v>
       </c>
       <c r="C45">
         <v>240.80649437282904</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>19.305643632053229</v>
+        <v>19.249626388417198</v>
       </c>
       <c r="B46">
-        <v>-6.2407875192055684</v>
+        <v>-6.40593874308822</v>
       </c>
       <c r="C46">
         <v>240.80649437282904</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>18.223812918433872</v>
+        <v>18.176104546220195</v>
       </c>
       <c r="B47">
-        <v>-5.9110288710917978</v>
+        <v>-6.0494504401134117</v>
       </c>
       <c r="C47">
         <v>240.80649437282904</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>17.141834600416747</v>
+        <v>17.102158460565498</v>
       </c>
       <c r="B48">
-        <v>-5.5817680637145477</v>
+        <v>-5.694330369363052</v>
       </c>
       <c r="C48">
         <v>240.80649437282904</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>16.0595402732289</v>
+        <v>16.027671274464545</v>
       </c>
       <c r="B49">
-        <v>-5.2535730934035891</v>
+        <v>-5.3409554075915207</v>
       </c>
       <c r="C49">
         <v>240.80649437282904</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>14.976761532097388</v>
+        <v>14.952526130928764</v>
       </c>
       <c r="B50">
-        <v>-4.9270119564886912</v>
+        <v>-4.9897024315531979</v>
       </c>
       <c r="C50">
         <v>240.80649437282904</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>13.89337934770677</v>
+        <v>13.876640462328355</v>
       </c>
       <c r="B51">
-        <v>-4.6024861155479888</v>
+        <v>-4.6408377310158073</v>
       </c>
       <c r="C51">
         <v>240.80649437282904</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>12.809472192571521</v>
+        <v>12.800068858468494</v>
       </c>
       <c r="B52">
-        <v>-4.2797308981530344</v>
+        <v>-4.2941852478004447</v>
       </c>
       <c r="C52">
         <v>240.80649437282904</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>11.725167914663617</v>
+        <v>11.722900198513109</v>
       </c>
       <c r="B53">
-        <v>-3.9583150981237423</v>
+        <v>-3.9494583367415497</v>
       </c>
       <c r="C53">
         <v>240.80649437282904</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>10.640594361955021</v>
+        <v>10.645223361626117</v>
       </c>
       <c r="B54">
-        <v>-3.6378075092800208</v>
+        <v>-3.6063703526735593</v>
       </c>
       <c r="C54">
         <v>240.80649437282904</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>9.55584875835126</v>
+        <v>9.5671059510412118</v>
       </c>
       <c r="B55">
-        <v>-3.3178802144225279</v>
+        <v>-3.2647032676667274</v>
       </c>
       <c r="C55">
         <v>240.80649437282904</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>8.4709058314920309</v>
+        <v>8.4885304662710439</v>
       </c>
       <c r="B56">
-        <v>-2.9986184522748669</v>
+        <v>-2.924513522734538</v>
       </c>
       <c r="C56">
         <v>240.80649437282904</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>7.3857096849505774</v>
+        <v>7.4094581308980292</v>
       </c>
       <c r="B57">
-        <v>-2.680210750541387</v>
+        <v>-2.5859261761262906</v>
       </c>
       <c r="C57">
         <v>240.80649437282904</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>6.3002044223001548</v>
+        <v>6.3298501685045814</v>
       </c>
       <c r="B58">
-        <v>-2.3628456369264357</v>
+        <v>-2.2490662860912853</v>
       </c>
       <c r="C58">
         <v>240.80649437282904</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5.2143408709558408</v>
+        <v>5.249672467603026</v>
       </c>
       <c r="B59">
-        <v>-2.0466889609321681</v>
+        <v>-1.9140438659621879</v>
       </c>
       <c r="C59">
         <v>240.80649437282904</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4.1280967537001185</v>
+        <v>4.1689095764254152</v>
       </c>
       <c r="B60">
-        <v>-1.7318158592519903</v>
+        <v>-1.580908749405163</v>
       </c>
       <c r="C60">
         <v>240.80649437282904</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3.0414565171573016</v>
+        <v>3.0875507081337159</v>
       </c>
       <c r="B61">
-        <v>-1.4182787903771155</v>
+        <v>-1.2496957251697429</v>
       </c>
       <c r="C61">
         <v>240.80649437282904</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1.9544046079517141</v>
+        <v>2.0055850758898996</v>
       </c>
       <c r="B62">
-        <v>-1.1061302127987596</v>
+        <v>-0.92043958200546261</v>
       </c>
       <c r="C62">
         <v>240.80649437282904</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.8669664816739403</v>
+        <v>0.923030371081374</v>
       </c>
       <c r="B63">
-        <v>-0.79528426979344458</v>
+        <v>-0.59308326322494287</v>
       </c>
       <c r="C63">
         <v>240.80649437282904</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.22066837022039321</v>
+        <v>-0.1599818020027417</v>
       </c>
       <c r="B64">
-        <v>-0.48510184377891585</v>
+        <v>-0.26720233039314256</v>
       </c>
       <c r="C64">
         <v>240.80649437282904</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.3082694473093854</v>
+        <v>-1.2432913608478815</v>
       </c>
       <c r="B65">
-        <v>-0.17480550195822872</v>
+        <v>0.057719500361890504</v>
       </c>
       <c r="C65">
         <v>240.80649437282904</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.3956062491711485</v>
+        <v>-2.3267382229394933</v>
       </c>
       <c r="B66">
-        <v>0.1363821884655651</v>
+        <v>0.382198512912112</v>
       </c>
       <c r="C66">
         <v>240.80649437282904</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.4827460699352044</v>
+        <v>-3.4103691500584161</v>
       </c>
       <c r="B67">
-        <v>0.44823425756803736</v>
+        <v>0.7060838953256805</v>
       </c>
       <c r="C67">
         <v>240.80649437282904</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-4.5709473819367821</v>
+        <v>-4.4950582811671174</v>
       </c>
       <c r="B68">
-        <v>0.7565061245392718</v>
+        <v>1.0265564524555857</v>
       </c>
       <c r="C68">
         <v>240.80649437282904</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-5.6611849024443615</v>
+        <v>-5.5814826731126939</v>
       </c>
       <c r="B69">
-        <v>1.0579102588574585</v>
+        <v>1.3414326008447728</v>
       </c>
       <c r="C69">
         <v>240.80649437282904</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-6.7521071502537673</v>
+        <v>-6.6687036770991828</v>
       </c>
       <c r="B70">
-        <v>1.3570049420387185</v>
+        <v>1.6537395870112002</v>
       </c>
       <c r="C70">
         <v>240.80649437282904</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-7.8422406320315927</v>
+        <v>-7.7556979028578086</v>
       </c>
       <c r="B71">
-        <v>1.6587599786242364</v>
+        <v>1.9667779581254457</v>
       </c>
       <c r="C71">
         <v>240.80649437282904</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-8.9319500044001146</v>
+        <v>-8.8427186998715754</v>
       </c>
       <c r="B72">
-        <v>1.9619454532175209</v>
+        <v>2.2797306339935597</v>
       </c>
       <c r="C72">
         <v>240.80649437282904</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-10.021844498880673</v>
+        <v>-9.9301892980851356</v>
       </c>
       <c r="B73">
-        <v>2.2645065471691033</v>
+        <v>2.5912326510831076</v>
       </c>
       <c r="C73">
         <v>240.80649437282904</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-11.111673496635115</v>
+        <v>-11.017935709537955</v>
       </c>
       <c r="B74">
-        <v>2.5672885487552812</v>
+        <v>2.9018451398722465</v>
       </c>
       <c r="C74">
         <v>240.80649437282904</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-12.200966711688889</v>
+        <v>-12.105631376807152</v>
       </c>
       <c r="B75">
-        <v>2.8718776404982256</v>
+        <v>3.2126212842840585</v>
       </c>
       <c r="C75">
         <v>240.80649437282904</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-13.289235039881305</v>
+        <v>-13.19293668252566</v>
       </c>
       <c r="B76">
-        <v>3.1799234749778242</v>
+        <v>3.524656388010746</v>
       </c>
       <c r="C76">
         <v>240.80649437282904</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-14.376025612095367</v>
+        <v>-14.279537182620565</v>
       </c>
       <c r="B77">
-        <v>3.4929534910654723</v>
+        <v>3.8389645680776647</v>
       </c>
       <c r="C77">
         <v>240.80649437282904</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-15.461049317575005</v>
+        <v>-15.365232186139778</v>
       </c>
       <c r="B78">
-        <v>3.811942802740877</v>
+        <v>4.1561930750736567</v>
       </c>
       <c r="C78">
         <v>240.80649437282904</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-16.543813531794342</v>
+        <v>-16.449679652071573</v>
       </c>
       <c r="B79">
-        <v>4.1385529360865263</v>
+        <v>4.4774450292138628</v>
       </c>
       <c r="C79">
         <v>240.80649437282904</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-17.623454228859877</v>
+        <v>-17.532279584152796</v>
       </c>
       <c r="B80">
-        <v>4.475698081286934</v>
+        <v>4.8046554850215912</v>
       </c>
       <c r="C80">
         <v>240.80649437282904</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-18.697850050747814</v>
+        <v>-18.611558685465752</v>
       </c>
       <c r="B81">
-        <v>4.830533163648596</v>
+        <v>5.1425759885310933</v>
       </c>
       <c r="C81">
         <v>240.80649437282904</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-19.728809724786526</v>
+        <v>-19.660990497427413</v>
       </c>
       <c r="B82">
-        <v>5.33186986901567</v>
+        <v>5.5767573120064879</v>
       </c>
       <c r="C82">
         <v>240.80649437282904</v>
